--- a/stories/arbres/TREE-JEU-004.xlsx
+++ b/stories/arbres/TREE-JEU-004.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Lina est à la ferme, avec maman. On joue à un petit jeu de sacs de graines. Maman gagne une fois. L'autre peut gagner. Lina est déçue. Son ventre se serre. Être déçu, c'est permis. Lina dit bravo. Maman dit : on peut rejouer plus tard. Perdre, ce n'est pas être moins gentil. On respire. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard.</t>
+          <t>Lina est à la ferme, avec maman. On joue à un petit jeu de sacs de graines. Maman gagne une fois. L'autre peut gagner. Lina est déçue. Son ventre se serre. Être déçu, c'est permis. Lina dit bravo. On peut rejouer plus tard. Perdre, ce n'est pas être moins gentil. On respire. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,12 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Lina est à la ferme, avec maman. On joue à un petit jeu de sacs de graines. Maman gagne une fois. L'autre peut gagner. Lina est déçue. Son ventre se serre. Être déçu, c'est permis. Lina dit bravo.
+maman|On peut rejouer plus tard. Perdre, ce n'est pas être moins gentil. On respire. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1510,11 @@
         <v>12</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1649,6 +1677,11 @@
         <v>12</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Lina va vers la cuisine de la ferme. Un jeu de gobelets. Papa gagnerait peut-être. L'autre peut gagner. Déçue, c'est permis. Rejouer plus tard. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1862,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|L'autre a gagné. On peut être quoi ?</t>
         </is>
       </c>
     </row>
@@ -1997,6 +2035,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Lina a dit bravo. L'autre peut gagner. Déçu, permis. Rejouer plus tard. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2183,6 +2226,11 @@
         <v>12</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2345,6 +2393,11 @@
         <v>12</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Lina prend le ballon rouge. Le lait est froid dans le verre. Lina pose le ballon. Une partie. L'autre peut gagner. Déçu, permis. Rejouer plus tard. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2533,6 +2586,11 @@
       <c r="AV9" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -2697,6 +2755,11 @@
         <v>12</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Tom. La lumière est claire. On feuillette le livre. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. On a dit bravo. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Lina dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2859,6 +2922,11 @@
         <v>12</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3021,6 +3089,11 @@
         <v>12</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Léa. Des miettes dorment sur la table. On referme le livre. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Le ventre est plus calme. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Maman serre Lina tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3183,6 +3256,11 @@
         <v>12</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3345,6 +3423,11 @@
         <v>12</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Sami. Un chat miaule une fois. On pose le ballon. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Le jeu est rangé. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Papa n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3507,6 +3590,11 @@
         <v>12</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3669,6 +3757,11 @@
         <v>12</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Lina prend le seau bleu. Le sol est un peu frais. Le seau sert de but. Maman marque. L'autre peut gagner. Lina dit bravo. Rejouer plus tard. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3859,6 +3952,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3883,7 +3981,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Lina rejoint Tom. Les chaussures font toc toc. On secoue le sable. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. On se tient la main. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Lina range. Maman dit : c'est bien.</t>
+          <t>Lina rejoint Tom. Les chaussures font toc toc. On secoue le sable. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. On se tient la main. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Lina range. C'est bien.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4021,6 +4119,12 @@
         <v>12</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Tom. Les chaussures font toc toc. On secoue le sable. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. On se tient la main. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Lina range.
+maman|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4183,6 +4287,11 @@
         <v>12</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4345,6 +4454,11 @@
         <v>12</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Léa. La couverture est douce. On caresse le tissu. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. On a dit bravo. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. On souffle. Lina sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4507,6 +4621,11 @@
         <v>12</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4669,6 +4788,11 @@
         <v>12</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Sami. Une cloche tinte au loin. On tend la main. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Le ventre est plus calme. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Lina prend la main de maman.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4831,6 +4955,11 @@
         <v>12</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4993,6 +5122,11 @@
         <v>12</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Lina prend le doudou. Le banc est lisse. Le doudou a 'gagné'. Lina sourit un peu. Déçu, permis. L'autre peut gagner. Rejouer plus tard. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5181,6 +5315,11 @@
       <c r="AV25" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -5345,6 +5484,11 @@
         <v>12</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Tom. Le bois sent le chaud. On chante un petit air. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Le jeu est rangé. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Lina dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5507,6 +5651,11 @@
         <v>12</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5669,6 +5818,11 @@
         <v>12</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Léa. Une goutte tombe, ploc. On compte jusqu'à trois. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. On se tient la main. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Maman serre Lina tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5831,6 +5985,11 @@
         <v>12</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5993,6 +6152,11 @@
         <v>12</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Sami. Le savon sent la fleur. On montre du doigt. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. On a dit bravo. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Papa n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6155,6 +6319,11 @@
         <v>12</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6317,6 +6486,11 @@
         <v>12</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Lina va vers le jardin. Course de plumes. La plume de maman arrive avant. L'autre peut gagner. Lina souffle. Déçu, permis. On peut rejouer plus tard. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6493,6 +6667,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Après, on peut faire quoi ?</t>
         </is>
       </c>
     </row>
@@ -6661,6 +6840,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Le ventre s'est desserré. Rejouer plus tard. L'autre peut gagner. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6847,6 +7031,11 @@
         <v>12</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7009,6 +7198,11 @@
         <v>12</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Lina prend le ballon rouge. Un nuage passe lentement. Le ballon s'arrête. Lina respire. L'autre peut gagner. Rejouer plus tard. Déçu, permis. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7199,6 +7393,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7223,7 +7422,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Lina rejoint Tom. Le tissu est tout doux. On range la chaise. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Le ventre est plus calme. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Lina range. Maman dit : c'est bien.</t>
+          <t>Lina rejoint Tom. Le tissu est tout doux. On range la chaise. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Le ventre est plus calme. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Lina range. C'est bien.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7361,6 +7560,12 @@
         <v>12</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Tom. Le tissu est tout doux. On range la chaise. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Le ventre est plus calme. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Lina range.
+maman|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7523,6 +7728,11 @@
         <v>12</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7685,6 +7895,11 @@
         <v>12</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Léa. Une cuillère tinte. On range un objet. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Le jeu est rangé. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. On souffle. Lina sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7847,6 +8062,11 @@
         <v>12</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8009,6 +8229,11 @@
         <v>12</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Sami. Le sable est tiède. On se tient la main. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. On se tient la main. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Lina prend la main de maman.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8171,6 +8396,11 @@
         <v>12</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8333,6 +8563,11 @@
         <v>12</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Lina prend le seau bleu. Le vent est doux sur la joue. Lina pose le seau. Bravo. L'autre peut gagner. Rejouer plus tard. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8521,6 +8756,11 @@
       <c r="AV45" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -8685,6 +8925,11 @@
         <v>12</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Tom. Un rire court, tout petit. On dit merci. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. On a dit bravo. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Lina dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8847,6 +9092,11 @@
         <v>12</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9009,6 +9259,11 @@
         <v>12</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Léa. Le papier froisse, chut. On souffle doucement. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Le ventre est plus calme. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Maman serre Lina tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9171,6 +9426,11 @@
         <v>12</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9333,6 +9593,11 @@
         <v>12</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Sami. L'herbe chatouille le mollet. On écoute jusqu'au bout. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Le jeu est rangé. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Papa n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9495,6 +9760,11 @@
         <v>12</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9657,6 +9927,11 @@
         <v>12</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Lina prend le doudou. Le banc est lisse. Lina câline le doudou. Déçu, permis. L'autre peut gagner. Rejouer plus tard. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9847,6 +10122,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9871,7 +10151,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Lina rejoint Tom. Un pigeon roucoule. On attend son tour. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. On se tient la main. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Lina range. Maman dit : c'est bien.</t>
+          <t>Lina rejoint Tom. Un pigeon roucoule. On attend son tour. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. On se tient la main. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Lina range. C'est bien.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10009,6 +10289,12 @@
         <v>12</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Tom. Un pigeon roucoule. On attend son tour. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. On se tient la main. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Lina range.
+maman|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10171,6 +10457,11 @@
         <v>12</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10333,6 +10624,11 @@
         <v>12</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Léa. La fenêtre vibre un peu. On sourit ensemble. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. On a dit bravo. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. On souffle. Lina sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10495,6 +10791,11 @@
         <v>12</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10657,6 +10958,11 @@
         <v>12</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Sami. Le lait est froid dans le verre. On pose les pieds par terre. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Le ventre est plus calme. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Lina prend la main de maman.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10819,6 +11125,11 @@
         <v>12</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10981,6 +11292,11 @@
         <v>12</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Lina va vers la chambre des invités. Un puzzle. Maman place la dernière pièce. L'autre peut gagner. Lina dit bravo. Rejouer plus tard. Déçu, permis. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11157,6 +11473,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Qui peut gagner ?</t>
         </is>
       </c>
     </row>
@@ -11325,6 +11646,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Maman serre la main. Déçu, permis. Rejouer plus tard. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11511,6 +11837,11 @@
         <v>12</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11673,6 +12004,11 @@
         <v>12</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Lina prend le ballon rouge. Un vélo passe, toc toc. Encore une manche ? Plus tard. L'autre peut gagner. Déçu, permis. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11861,6 +12197,11 @@
       <c r="AV65" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -12025,6 +12366,11 @@
         <v>12</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Tom. La corde du sac est rêche. On parle tout bas. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Le jeu est rangé. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Lina dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12187,6 +12533,11 @@
         <v>12</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12349,6 +12700,11 @@
         <v>12</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Léa. Le savon mousse entre les doigts. On range les jouets. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. On se tient la main. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Maman serre Lina tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12511,6 +12867,11 @@
         <v>12</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12673,6 +13034,11 @@
         <v>12</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Sami. Un ruisseau chante. On s'assoit un moment. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. On a dit bravo. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Papa n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12835,6 +13201,11 @@
         <v>12</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12859,7 +13230,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Lina prend le seau bleu. Un ruisseau chante. Le seau est rangé. Lina dit : rejouer plus tard. L'autre peut gagner. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard.</t>
+          <t>Lina prend le seau bleu. Un ruisseau chante. Le seau est rangé. Rejouer plus tard. L'autre peut gagner. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -12997,6 +13368,12 @@
         <v>12</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Lina prend le seau bleu. Un ruisseau chante. Le seau est rangé.
+enfant-f|Rejouer plus tard. L'autre peut gagner. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13187,6 +13564,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13211,7 +13593,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Lina rejoint Tom. La laine gratte un peu. On respire, un, deux. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Le ventre est plus calme. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Lina range. Maman dit : c'est bien.</t>
+          <t>Lina rejoint Tom. La laine gratte un peu. On respire, un, deux. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Le ventre est plus calme. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Lina range. C'est bien.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13349,6 +13731,12 @@
         <v>12</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Tom. La laine gratte un peu. On respire, un, deux. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Le ventre est plus calme. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Lina range.
+maman|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13511,6 +13899,11 @@
         <v>12</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13673,6 +14066,11 @@
         <v>12</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Léa. Un pain croustille. On referme le sac. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Le jeu est rangé. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. On souffle. Lina sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13835,6 +14233,11 @@
         <v>12</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13997,6 +14400,11 @@
         <v>12</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Sami. Le savon glisse. On essuie une miette. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. On se tient la main. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Lina prend la main de maman.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14159,6 +14567,11 @@
         <v>12</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14321,6 +14734,11 @@
         <v>12</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Lina prend le doudou. Le papier froisse, chut. Le doudou écoute. Déçu, permis. Bravo. Rejouer plus tard. L'autre peut gagner. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14509,6 +14927,11 @@
       <c r="AV81" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -14673,6 +15096,11 @@
         <v>12</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Tom. Une plume vole. On met le doudou près. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. On a dit bravo. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Lina dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14835,6 +15263,11 @@
         <v>12</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14997,6 +15430,11 @@
         <v>12</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Léa. Le banc est lisse. On lace les chaussures. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Le ventre est plus calme. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Maman serre Lina tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15159,6 +15597,11 @@
         <v>12</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15321,6 +15764,11 @@
         <v>12</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Sami. Un grelot sonne. On met le manteau. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Le jeu est rangé. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Papa n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15483,6 +15931,11 @@
         <v>12</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15501,7 +15954,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15574,6 +16027,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>ch3C3: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-JEU-004.xlsx
+++ b/stories/arbres/TREE-JEU-004.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1324,6 +1329,7 @@
 maman|On peut rejouer plus tard. Perdre, ce n'est pas être moins gentil. On respire. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1515,6 +1521,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1682,6 +1689,7 @@
           <t>narrateur|Lina va vers la cuisine de la ferme. Un jeu de gobelets. Papa gagnerait peut-être. L'autre peut gagner. Déçue, c'est permis. Rejouer plus tard. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1869,6 +1877,7 @@
           <t>narrateur|L'autre a gagné. On peut être quoi ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2040,6 +2049,7 @@
           <t>narrateur|Lina a dit bravo. L'autre peut gagner. Déçu, permis. Rejouer plus tard. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2231,6 +2241,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2398,6 +2409,7 @@
           <t>narrateur|Lina prend le ballon rouge. Le lait est froid dans le verre. Lina pose le ballon. Une partie. L'autre peut gagner. Déçu, permis. Rejouer plus tard. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2593,6 +2605,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2760,6 +2773,7 @@
           <t>narrateur|Lina rejoint Tom. La lumière est claire. On feuillette le livre. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. On a dit bravo. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Lina dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2927,6 +2941,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3094,6 +3109,7 @@
           <t>narrateur|Lina rejoint Léa. Des miettes dorment sur la table. On referme le livre. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Le ventre est plus calme. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Maman serre Lina tout doux.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3261,6 +3277,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3428,6 +3445,7 @@
           <t>narrateur|Lina rejoint Sami. Un chat miaule une fois. On pose le ballon. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Le jeu est rangé. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Papa n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3595,6 +3613,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3762,6 +3781,7 @@
           <t>narrateur|Lina prend le seau bleu. Le sol est un peu frais. Le seau sert de but. Maman marque. L'autre peut gagner. Lina dit bravo. Rejouer plus tard. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3957,6 +3977,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4125,6 +4146,7 @@
 maman|C'est bien.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4292,6 +4314,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4459,6 +4482,7 @@
           <t>narrateur|Lina rejoint Léa. La couverture est douce. On caresse le tissu. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. On a dit bravo. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. On souffle. Lina sourit.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4626,6 +4650,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4793,6 +4818,7 @@
           <t>narrateur|Lina rejoint Sami. Une cloche tinte au loin. On tend la main. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Le ventre est plus calme. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Lina prend la main de maman.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4960,6 +4986,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5127,6 +5154,7 @@
           <t>narrateur|Lina prend le doudou. Le banc est lisse. Le doudou a 'gagné'. Lina sourit un peu. Déçu, permis. L'autre peut gagner. Rejouer plus tard. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5322,6 +5350,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5489,6 +5518,7 @@
           <t>narrateur|Lina rejoint Tom. Le bois sent le chaud. On chante un petit air. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Le jeu est rangé. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Lina dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5656,6 +5686,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5823,6 +5854,7 @@
           <t>narrateur|Lina rejoint Léa. Une goutte tombe, ploc. On compte jusqu'à trois. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. On se tient la main. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Maman serre Lina tout doux.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5990,6 +6022,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6157,6 +6190,7 @@
           <t>narrateur|Lina rejoint Sami. Le savon sent la fleur. On montre du doigt. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. On a dit bravo. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Papa n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6324,6 +6358,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6491,6 +6526,7 @@
           <t>narrateur|Lina va vers le jardin. Course de plumes. La plume de maman arrive avant. L'autre peut gagner. Lina souffle. Déçu, permis. On peut rejouer plus tard. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6674,6 +6710,7 @@
           <t>narrateur|Après, on peut faire quoi ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6845,6 +6882,7 @@
           <t>narrateur|Le ventre s'est desserré. Rejouer plus tard. L'autre peut gagner. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7036,6 +7074,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7203,6 +7242,7 @@
           <t>narrateur|Lina prend le ballon rouge. Un nuage passe lentement. Le ballon s'arrête. Lina respire. L'autre peut gagner. Rejouer plus tard. Déçu, permis. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7398,6 +7438,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7566,6 +7607,7 @@
 maman|C'est bien.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7733,6 +7775,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7900,6 +7943,7 @@
           <t>narrateur|Lina rejoint Léa. Une cuillère tinte. On range un objet. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Le jeu est rangé. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. On souffle. Lina sourit.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8067,6 +8111,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8234,6 +8279,7 @@
           <t>narrateur|Lina rejoint Sami. Le sable est tiède. On se tient la main. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. On se tient la main. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Lina prend la main de maman.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8401,6 +8447,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8568,6 +8615,7 @@
           <t>narrateur|Lina prend le seau bleu. Le vent est doux sur la joue. Lina pose le seau. Bravo. L'autre peut gagner. Rejouer plus tard. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8763,6 +8811,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8930,6 +8979,7 @@
           <t>narrateur|Lina rejoint Tom. Un rire court, tout petit. On dit merci. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. On a dit bravo. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Lina dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9097,6 +9147,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9264,6 +9315,7 @@
           <t>narrateur|Lina rejoint Léa. Le papier froisse, chut. On souffle doucement. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Le ventre est plus calme. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Maman serre Lina tout doux.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9431,6 +9483,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9598,6 +9651,7 @@
           <t>narrateur|Lina rejoint Sami. L'herbe chatouille le mollet. On écoute jusqu'au bout. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Le jeu est rangé. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Papa n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9765,6 +9819,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9932,6 +9987,7 @@
           <t>narrateur|Lina prend le doudou. Le banc est lisse. Lina câline le doudou. Déçu, permis. L'autre peut gagner. Rejouer plus tard. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10127,6 +10183,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10295,6 +10352,7 @@
 maman|C'est bien.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10462,6 +10520,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10629,6 +10688,7 @@
           <t>narrateur|Lina rejoint Léa. La fenêtre vibre un peu. On sourit ensemble. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. On a dit bravo. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. On souffle. Lina sourit.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10796,6 +10856,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10963,6 +11024,7 @@
           <t>narrateur|Lina rejoint Sami. Le lait est froid dans le verre. On pose les pieds par terre. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Le ventre est plus calme. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Lina prend la main de maman.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11130,6 +11192,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11297,6 +11360,7 @@
           <t>narrateur|Lina va vers la chambre des invités. Un puzzle. Maman place la dernière pièce. L'autre peut gagner. Lina dit bravo. Rejouer plus tard. Déçu, permis. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11480,6 +11544,7 @@
           <t>narrateur|Qui peut gagner ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11651,6 +11716,7 @@
           <t>narrateur|Maman serre la main. Déçu, permis. Rejouer plus tard. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11842,6 +11908,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12009,6 +12076,7 @@
           <t>narrateur|Lina prend le ballon rouge. Un vélo passe, toc toc. Encore une manche ? Plus tard. L'autre peut gagner. Déçu, permis. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12204,6 +12272,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12371,6 +12440,7 @@
           <t>narrateur|Lina rejoint Tom. La corde du sac est rêche. On parle tout bas. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Le jeu est rangé. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Lina dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12538,6 +12608,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12705,6 +12776,7 @@
           <t>narrateur|Lina rejoint Léa. Le savon mousse entre les doigts. On range les jouets. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. On se tient la main. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Maman serre Lina tout doux.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12872,6 +12944,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13039,6 +13112,7 @@
           <t>narrateur|Lina rejoint Sami. Un ruisseau chante. On s'assoit un moment. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. On a dit bravo. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Papa n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13206,6 +13280,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13374,6 +13449,7 @@
 enfant-f|Rejouer plus tard. L'autre peut gagner. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13569,6 +13645,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13737,6 +13814,7 @@
 maman|C'est bien.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13904,6 +13982,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14071,6 +14150,7 @@
           <t>narrateur|Lina rejoint Léa. Un pain croustille. On referme le sac. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Le jeu est rangé. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. On souffle. Lina sourit.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14238,6 +14318,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14405,6 +14486,7 @@
           <t>narrateur|Lina rejoint Sami. Le savon glisse. On essuie une miette. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. On se tient la main. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Lina prend la main de maman.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14572,6 +14654,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14739,6 +14822,7 @@
           <t>narrateur|Lina prend le doudou. Le papier froisse, chut. Le doudou écoute. Déçu, permis. Bravo. Rejouer plus tard. L'autre peut gagner. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14934,6 +15018,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15101,6 +15186,7 @@
           <t>narrateur|Lina rejoint Tom. Une plume vole. On met le doudou près. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. On a dit bravo. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Lina dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15268,6 +15354,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15435,6 +15522,7 @@
           <t>narrateur|Lina rejoint Léa. Le banc est lisse. On lace les chaussures. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Le ventre est plus calme. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Maman serre Lina tout doux.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15602,6 +15690,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15769,6 +15858,7 @@
           <t>narrateur|Lina rejoint Sami. Un grelot sonne. On met le manteau. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Le jeu est rangé. L'autre peut gagner. Être déçu, c'est permis. On peut rejouer plus tard. Papa n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15936,6 +16026,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15954,7 +16045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16034,6 +16125,20 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16048,7 +16153,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16235,6 +16340,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
